--- a/artfynd/A 61396-2021 artfynd.xlsx
+++ b/artfynd/A 61396-2021 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136146808</v>
       </c>
       <c r="B2" t="n">
-        <v>57867</v>
+        <v>57868</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -799,7 +799,7 @@
         <v>136146809</v>
       </c>
       <c r="B3" t="n">
-        <v>57867</v>
+        <v>57868</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 61396-2021 artfynd.xlsx
+++ b/artfynd/A 61396-2021 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136146808</v>
       </c>
       <c r="B2" t="n">
-        <v>57868</v>
+        <v>57872</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -799,7 +799,7 @@
         <v>136146809</v>
       </c>
       <c r="B3" t="n">
-        <v>57868</v>
+        <v>57872</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 61396-2021 artfynd.xlsx
+++ b/artfynd/A 61396-2021 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136146808</v>
       </c>
       <c r="B2" t="n">
-        <v>57872</v>
+        <v>57873</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -799,7 +799,7 @@
         <v>136146809</v>
       </c>
       <c r="B3" t="n">
-        <v>57872</v>
+        <v>57873</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 61396-2021 artfynd.xlsx
+++ b/artfynd/A 61396-2021 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136146808</v>
       </c>
       <c r="B2" t="n">
-        <v>57873</v>
+        <v>57878</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -799,7 +799,7 @@
         <v>136146809</v>
       </c>
       <c r="B3" t="n">
-        <v>57873</v>
+        <v>57878</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 61396-2021 artfynd.xlsx
+++ b/artfynd/A 61396-2021 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136146808</v>
       </c>
       <c r="B2" t="n">
-        <v>57878</v>
+        <v>57891</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -799,7 +799,7 @@
         <v>136146809</v>
       </c>
       <c r="B3" t="n">
-        <v>57878</v>
+        <v>57891</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
